--- a/excel/distribuidora-sol-del-valle-s-a-c_ccc.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_ccc.xlsx
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>35477</v>
+        <v>98200</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C001413893</t>
+          <t>C004196674</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
+          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17784549</t>
+          <t>S17774878</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1421,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49498</v>
+        <v>35477</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C001739071</t>
+          <t>C001413893</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17786972</t>
+          <t>S17784549</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>52398</v>
+        <v>49498</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C001733224</t>
+          <t>C001739071</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
+          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17771910</t>
+          <t>S17786972</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>28551</v>
+        <v>52398</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C001612754</t>
+          <t>C001733224</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C001612754 - GAVIDIA VARGAS ELIZABETH AURORA</t>
+          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17779762</t>
+          <t>S17771910</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98200</v>
+        <v>28551</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C004196674</t>
+          <t>C001612754</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
+          <t>C001612754 - GAVIDIA VARGAS ELIZABETH AURORA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>S17774878</t>
+          <t>S17779762</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1885,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109603</v>
+        <v>18132</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C001400565</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S17782189</t>
+          <t>S17778382</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88870</v>
+        <v>50129</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C001645160</t>
+          <t>C001732191</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C001645160 - GOMEZ UGARTE ROSA</t>
+          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2060,11 +2060,11 @@
         <v>46235</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>S17769426</t>
+          <t>S17750266</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2095,7 +2095,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
@@ -2117,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>92686</v>
+        <v>109603</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2151,12 +2155,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C004183506</t>
+          <t>C001740647</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2176,11 +2180,11 @@
         <v>46235</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>S17752135</t>
+          <t>S17782189</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2203,7 +2207,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2221,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>74273</v>
+        <v>88870</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2267,12 +2271,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C004171449</t>
+          <t>C001645160</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C004171449 - CRUZ QUISPE ETHEL MELIZA</t>
+          <t>C001645160 - GOMEZ UGARTE ROSA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2292,11 +2296,11 @@
         <v>46235</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17754673</t>
+          <t>S17769426</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2319,7 +2323,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2342,14 +2346,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18132</v>
+        <v>92686</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2383,12 +2387,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C004183506</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2408,11 +2412,11 @@
         <v>46235</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17778382</t>
+          <t>S17752135</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2435,7 +2439,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2453,7 +2457,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2469,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>50129</v>
+        <v>74273</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2499,12 +2503,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C001732191</t>
+          <t>C004171449</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+          <t>C004171449 - CRUZ QUISPE ETHEL MELIZA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2528,7 +2532,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17750266</t>
+          <t>S17754673</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2559,11 +2563,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98178</v>
+        <v>13175</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C001761062</t>
+          <t>C001370989</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C001761062 - CERNA PRIETO MARTINA</t>
+          <t>C001370989 - ESQUIVEL ENRIQUEZ TEODOLINDA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2760,11 +2760,11 @@
         <v>46235</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17702419</t>
+          <t>S17747018</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13175</v>
+        <v>21521</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001370989</t>
+          <t>C001455878</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001370989 - ESQUIVEL ENRIQUEZ TEODOLINDA</t>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2876,11 +2876,11 @@
         <v>46235</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17747018</t>
+          <t>S17700213</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2890,11 +2890,11 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+          <t>41839652HUAMACHUCOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2933,7 +2933,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21521</v>
+        <v>42501</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001521872</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2992,11 +2992,11 @@
         <v>46235</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17700213</t>
+          <t>S17816038</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3006,11 +3006,11 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>41839652HUAMACHUCOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3049,7 +3049,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>42501</v>
+        <v>98178</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C001521872</t>
+          <t>C001761062</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
+          <t>C001761062 - CERNA PRIETO MARTINA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3108,11 +3108,11 @@
         <v>46235</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17816038</t>
+          <t>S17702419</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3165,7 +3165,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20947</v>
+        <v>68382</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3199,12 +3199,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C001448981</t>
+          <t>C004049198</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3224,11 +3224,11 @@
         <v>46235</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17614008</t>
+          <t>S17778706</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3397,7 +3397,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>68382</v>
+        <v>72180</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C004049198</t>
+          <t>C004183620</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3456,11 +3456,11 @@
         <v>46235</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17778706</t>
+          <t>S17816852</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3629,7 +3629,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>72180</v>
+        <v>20947</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C004183620</t>
+          <t>C001448981</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3688,11 +3688,11 @@
         <v>46235</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17816852</t>
+          <t>S17614008</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3745,7 +3745,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>84744</v>
+        <v>8301</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C004060767</t>
+          <t>C001128320</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3804,11 +3804,11 @@
         <v>46235</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17595528</t>
+          <t>S17722572</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109406</v>
+        <v>44037</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C004240756</t>
+          <t>C001674629</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3920,11 +3920,11 @@
         <v>46235</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17595832</t>
+          <t>S17628124</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3977,7 +3977,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8301</v>
+        <v>84744</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C001128320</t>
+          <t>C004060767</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4036,11 +4036,11 @@
         <v>46235</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46242</v>
+        <v>46238</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17722572</t>
+          <t>S17595528</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4093,7 +4093,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>44037</v>
+        <v>109406</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C001674629</t>
+          <t>C004240756</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4152,11 +4152,11 @@
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17628124</t>
+          <t>S17595832</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>37500</v>
+        <v>111263</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C001129172</t>
+          <t>C001706144</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
+          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17563528</t>
+          <t>S17565306</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4325,7 +4325,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14971</v>
+        <v>85084</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C004242198</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4384,11 +4384,11 @@
         <v>46235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17625290</t>
+          <t>S17555451</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4441,7 +4441,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111263</v>
+        <v>92441</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C001706144</t>
+          <t>C004200980</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
+          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17565306</t>
+          <t>S17566746</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>85084</v>
+        <v>74984</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C004242198</t>
+          <t>C004192601</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4616,11 +4616,11 @@
         <v>46235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17555451</t>
+          <t>S17628453</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Problemas con el despacho</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4666,14 +4666,14 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>92441</v>
+        <v>37500</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C004200980</t>
+          <t>C001129172</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
+          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17566746</t>
+          <t>S17563528</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>74984</v>
+        <v>14971</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17628453</t>
+          <t>S17625290</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Problemas con el despacho</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>

--- a/excel/distribuidora-sol-del-valle-s-a-c_ccc.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_ccc.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CCC" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CCC'!$A$1:$AB$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CCC'!$A$1:$AB$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AB84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58203</v>
+        <v>94227</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -643,12 +643,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C004166670</t>
+          <t>C004167425</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
+          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -662,17 +662,17 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="M2" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>S17857703</t>
+          <t>S18090254</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,7 +725,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18756</v>
+        <v>50217</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -759,12 +759,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C001401840</t>
+          <t>C001572723</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
+          <t>C001572723 - LIÑAN TORRES ASUNCION ROSMERY</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -778,17 +778,17 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="M3" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>S17843390</t>
+          <t>S18100757</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -841,7 +841,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>28221</v>
+        <v>40695</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -875,12 +875,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>C001567587</t>
+          <t>C001559213</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
+          <t>C001559213 - RUIZ ESPINOZA DELIA ISABEL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -894,17 +894,17 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>S17842952</t>
+          <t>S18104122</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -957,7 +957,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14036</v>
+        <v>98692</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C001367258</t>
+          <t>C004185437</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
+          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1010,17 +1010,17 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>S17840611</t>
+          <t>S18061538</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1061,19 +1061,19 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9702</v>
+        <v>101530</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>C001127634</t>
+          <t>C004197150</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C001127634 - VIDAL GARCIA TERESA</t>
+          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1126,17 +1126,17 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>46247</v>
+        <v>46254</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>S17844696</t>
+          <t>S18065179</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1182,14 +1182,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55524</v>
+        <v>67527</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C001736497</t>
+          <t>C004048840</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C001736497 - VILLENA BECERRA SHUSEY ESTEFANY</t>
+          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1242,17 +1242,17 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46246</v>
+        <v>46255</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>S17812905</t>
+          <t>S18074257</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1298,14 +1298,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98200</v>
+        <v>58800</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>C004196674</t>
+          <t>C001732698</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
+          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1358,17 +1358,17 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>S17774878</t>
+          <t>S18071097</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35477</v>
+        <v>25254</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C001413893</t>
+          <t>C001331142</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
+          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1474,17 +1474,17 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>S17784549</t>
+          <t>S18072558</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1537,7 +1537,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49498</v>
+        <v>17050</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C001739071</t>
+          <t>C001331147</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1590,17 +1590,17 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>46245</v>
+        <v>46254</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S17786972</t>
+          <t>S18062732</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1653,7 +1653,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>52398</v>
+        <v>36943</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C001733224</t>
+          <t>C001629991</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
+          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1706,17 +1706,17 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>S17771910</t>
+          <t>S18000291</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1769,7 +1769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>28551</v>
+        <v>61132</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>C001612754</t>
+          <t>C001711464</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C001612754 - GAVIDIA VARGAS ELIZABETH AURORA</t>
+          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1822,17 +1822,17 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>S17779762</t>
+          <t>S18102237</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1885,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>18132</v>
+        <v>68787</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C004054693</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1938,17 +1938,17 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="M13" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>S17778382</t>
+          <t>S18006105</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>50129</v>
+        <v>74771</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C001732191</t>
+          <t>C001563276</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2054,17 +2054,17 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>46244</v>
+        <v>46256</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>S17750266</t>
+          <t>S18100647</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2095,11 +2095,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
@@ -2121,7 +2117,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109603</v>
+        <v>103222</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2155,12 +2151,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C004199228</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2174,17 +2170,17 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>S17782189</t>
+          <t>S18106736</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2237,7 +2233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88870</v>
+        <v>104903</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2271,12 +2267,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C001645160</t>
+          <t>C004190467</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>C001645160 - GOMEZ UGARTE ROSA</t>
+          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2290,17 +2286,17 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>S17769426</t>
+          <t>S18004045</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2346,14 +2342,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>92686</v>
+        <v>26072</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2387,12 +2383,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C004183506</t>
+          <t>C001332822</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
+          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2406,17 +2402,17 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>46244</v>
+        <v>46255</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>S17752135</t>
+          <t>S18067791</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2439,7 +2435,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2457,7 +2453,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>74273</v>
+        <v>46317</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2503,12 +2499,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C004171449</t>
+          <t>C001682053</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C004171449 - CRUZ QUISPE ETHEL MELIZA</t>
+          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2522,17 +2518,17 @@
         </is>
       </c>
       <c r="L18" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>46244</v>
+        <v>46253</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>S17754673</t>
+          <t>S17995585</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2555,7 +2551,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2578,14 +2574,14 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>78878</v>
+        <v>31316</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2619,12 +2615,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C004224142</t>
+          <t>C001476009</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C004224142 - RAMIREZ FLORES ALEJANDRO DANIEL</t>
+          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2638,17 +2634,17 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>46242</v>
+        <v>46251</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46242</v>
+        <v>46253</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>S17723567</t>
+          <t>S18005147</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2671,7 +2667,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2701,7 +2697,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13175</v>
+        <v>41981</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2735,12 +2731,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C001370989</t>
+          <t>C001667496</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C001370989 - ESQUIVEL ENRIQUEZ TEODOLINDA</t>
+          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2754,17 +2750,17 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>S17747018</t>
+          <t>S17933339</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2787,7 +2783,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2805,7 +2801,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2817,7 +2813,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21521</v>
+        <v>63269</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2836,7 +2832,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2851,12 +2847,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001731770</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2870,17 +2866,17 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>S17700213</t>
+          <t>S18083957</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2890,11 +2886,11 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>41839652HUAMACHUCOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2903,7 +2899,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2933,7 +2929,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>42501</v>
+        <v>110981</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2967,12 +2963,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C001521872</t>
+          <t>C001733600</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
+          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2986,17 +2982,17 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>S17816038</t>
+          <t>S17926956</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3019,7 +3015,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3027,7 +3023,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
@@ -3049,7 +3049,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>98178</v>
+        <v>98632</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3083,12 +3083,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C001761062</t>
+          <t>C004182389</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C001761062 - CERNA PRIETO MARTINA</t>
+          <t>C004182389 - ZAVALETA ÑIQUE MARIA ELENA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3102,17 +3102,17 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>S17702419</t>
+          <t>S17942184</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quiere comparar precios antes de comprar</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3165,7 +3165,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>68382</v>
+        <v>79046</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3199,12 +3199,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C004049198</t>
+          <t>C004047558</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C004047558 - TRUJILLO ROJAS WILDER DANIEL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3218,17 +3218,17 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>S17778706</t>
+          <t>S17933985</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3281,7 +3281,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>68492</v>
+        <v>38233</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C004167730</t>
+          <t>C001533964</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
+          <t>C001533964 - LOPEZ CASANOVA MERCI NERI</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3334,17 +3334,17 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>S17620887</t>
+          <t>S17943772</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3390,14 +3390,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>72180</v>
+        <v>27637</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3431,12 +3431,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C004183620</t>
+          <t>C001371461</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+          <t>C001371461 - BAZAN MOYA LESLIE JULIANA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3450,17 +3450,17 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>S17816852</t>
+          <t>S17941567</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3513,7 +3513,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>72023</v>
+        <v>13625</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C004180942</t>
+          <t>C001125965</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C004180942 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C001125965 - PAISIG ALVA ANA MARIA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3566,17 +3566,17 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>46239</v>
+        <v>46249</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>S17778406</t>
+          <t>S17932132</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3629,7 +3629,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20947</v>
+        <v>15714</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>C001448981</t>
+          <t>C001125639</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+          <t>C001125639 - QUIROZ MARIN JUAN EDGARDO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3682,17 +3682,17 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>46239</v>
+        <v>46254</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>S17614008</t>
+          <t>S18042132</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3738,14 +3738,14 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8301</v>
+        <v>83170</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3779,12 +3779,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C001128320</t>
+          <t>C004061920</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+          <t>C004061920 - CARBAJAL PRETEL DANTE AMIN</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3798,17 +3798,17 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>46242</v>
+        <v>46254</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>S17722572</t>
+          <t>S18037060</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>44037</v>
+        <v>94180</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>C001674629</t>
+          <t>C004173978</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+          <t>C004173978 - ROMERO BUENO MARIA PILAR</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3914,17 +3914,17 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>S17628124</t>
+          <t>S17892771</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3970,14 +3970,14 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>84744</v>
+        <v>108915</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C004060767</t>
+          <t>C001117422</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+          <t>C001117422 - LIZARRAGA GUTIERREZ ANTERO DANIEL</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4030,17 +4030,17 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>S17595528</t>
+          <t>S17944749</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4093,7 +4093,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109406</v>
+        <v>110995</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C004240756</t>
+          <t>C001179290</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+          <t>C001179290 - CHIZA GUEVARA FLOR ANGELICA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4146,17 +4146,17 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>S17595832</t>
+          <t>S17944278</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4209,7 +4209,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111263</v>
+        <v>107111</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>C001706144</t>
+          <t>C004214056</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
+          <t>C004214056 - AMAYA CAMACHO CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4262,17 +4262,17 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>46237</v>
+        <v>46254</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>S17565306</t>
+          <t>S18045063</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4325,7 +4325,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>85084</v>
+        <v>87421</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>C004242198</t>
+          <t>C004166670</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4378,17 +4378,17 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>S17555451</t>
+          <t>S17857703</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4441,7 +4441,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>92441</v>
+        <v>49946</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C004200980</t>
+          <t>C001567587</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
+          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4494,17 +4494,17 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>S17566746</t>
+          <t>S17842952</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4557,7 +4557,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>74984</v>
+        <v>22591</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4591,12 +4591,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C001367258</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4610,17 +4610,17 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>S17628453</t>
+          <t>S17840611</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Problemas con el despacho</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4661,19 +4661,19 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37500</v>
+        <v>29237</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4707,12 +4707,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C001129172</t>
+          <t>C001401840</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
+          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4726,17 +4726,17 @@
         </is>
       </c>
       <c r="L37" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>S17563528</t>
+          <t>S17843390</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14971</v>
+        <v>14273</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C001127634</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C001127634 - VIDAL GARCIA TERESA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4842,17 +4842,17 @@
         </is>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>S17625290</t>
+          <t>S17844696</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4903,8 +4903,5348 @@
       </c>
       <c r="AB38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>47668</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>C001676187</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C001676187 - GOICOCHEA AREVALO JUAN JENINFER</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>S17937865</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>81</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>53283</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>C001711123</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C001711123 - LAIZA ZAVALETA ESTRELLITA NELLY</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>S18028555</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>81</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>87132</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>C004168393</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C004168393 - RODRIGUEZ VEGA GLORIA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>46250</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>S17921862</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>81</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>79047</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>C004047605</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C004047605 - VALVERDE VARGAS DE DAGA ROSITA INES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>46251</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>S17943006</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>81</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>61854</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>C001736497</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C001736497 - VILLENA BECERRA SHUSEY ESTEFANY</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>S17812905</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>81</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>75018</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>C001737285</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>S17979374</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>81</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>75447</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>C001739071</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>S17786972</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>81</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>76930</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>C001759977</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C001759977 - ARENAS VARGAS NAOMI STEPHANY</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>S17973645</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>81</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>83129</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>C004197916</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C004197916 - RAMIREZ GOMEZ LUISA FERNANDA MARICEL</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>S17974267</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>81</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>101416</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>C004196674</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>S17774878</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>81</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>53004</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>C001733224</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>S17771910</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>81</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>50429</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>C001612754</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>C001612754 - GAVIDIA VARGAS ELIZABETH AURORA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>S17779762</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>81</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>19180</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>C001413893</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>S17784549</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>81</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>27502</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>C001324650</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>S17869262</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>81</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>32730</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>C001400565</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>S17778382</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>81</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>107149</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>C004183506</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>S17752135</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>81</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>108567</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>C001740647</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>S17782189</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>81</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>87886</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>C004171449</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>C004171449 - CRUZ QUISPE ETHEL MELIZA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>S17754673</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>81</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>88364</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>C004168628</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>C004168628 - SILVA DOMINGUEZ HERNAN</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>46252</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>S17967496</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>81</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>86024</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>C001645160</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>C001645160 - GOMEZ UGARTE ROSA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>S17769426</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>81</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>61591</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>C001732191</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>S17750266</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>81</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>70618</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>C004169388</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C004169388 - JULCA REYES MARIA ROSMERIA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>S17921578</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>81</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>104809</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>C004224142</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C004224142 - RAMIREZ FLORES ALEJANDRO DANIEL</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>S17723567</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>81</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>21014</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>C001285138</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>46254</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>S18052111</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>81</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>22477</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>C001370989</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>C001370989 - ESQUIVEL ENRIQUEZ TEODOLINDA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>S17747018</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>81</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Iniciar sesión</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>29994</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>HUAMACHUCO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>C001455878</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>S17700213</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>41839652HUAMACHUCOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>116</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>25891</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>C001521872</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>S17816038</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>81</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>71471</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>C001761062</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C001761062 - CERNA PRIETO MARTINA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>S17702419</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>81</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>81755</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>C004200910</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>C004200910 - FERNANDEZ REYES JHENIFER VANESSA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>46241</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>S17994322</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>81</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>82957</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>C004049198</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>S17778706</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>81</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>98694</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>C004183620</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>S17816852</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>81</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>94262</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>C004167730</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>S17620887</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>81</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>96351</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>C004180942</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>C004180942 - ALFARO YUPANQUI EDUAR NILSON</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>S17778406</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>81</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>28205</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>C001444741</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>46253</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>S18004262</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>81</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>32452</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>C001448981</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="M73" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>S17614008</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>81</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>41696</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>C001640733</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>46249</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>S17917050</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>81</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>15956</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>C001128320</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M75" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>46242</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>S17722572</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>81</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>104905</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>C004240756</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>S17595832</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>81</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>109079</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>C001674629</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M77" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>S17628124</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>81</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>72540</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>C004060767</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>46238</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>S17595528</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>81</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>107164</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>C004200980</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>S17566746</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>81</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>102208</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>C004242198</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>S17555451</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>81</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>103503</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>C004192601</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M81" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>S17628453</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>81</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Problemas con el despacho</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>16999</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>C001129172</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M82" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>S17563528</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>81</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>20753</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>C001345662</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>46239</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>S17625290</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>81</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Tiene stock suficiente y quiere evitar sobre inventario.</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>50395</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FELIPE NERI CASTILLO PLASENCIA</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>41839652</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>C001706144</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>46235</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>S17565306</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>41839652TRUJILLOGIL MELGAREJO, OSCAR FERNANDO JUNIOR1000054785</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>81</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB38"/>
+  <autoFilter ref="A1:AB84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>